--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104587_W15.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104587_W15.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>F. GUERRA</t>
+          <t>R. GIEDRAITIS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4027</v>
+        <v>2.5275</v>
       </c>
       <c r="E2" t="n">
-        <v>1.6704</v>
+        <v>2.5274</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7322</v>
+        <v>0.0001</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.0436</v>
+        <v>-0.9383</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0548</v>
+        <v>0.2982</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9888</v>
+        <v>-1.2365</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8348</v>
+        <v>0.9665</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6856</v>
+        <v>0.7584</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1493</v>
+        <v>0.2081</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.8785</v>
+        <v>-1.9048</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.4603</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.1381</v>
+        <v>-1.4446</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1287</v>
+        <v>-0.0302</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8771</v>
+        <v>-0.3417</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2516</v>
+        <v>0.3115</v>
       </c>
       <c r="V2" t="n">
-        <v>1.8639</v>
+        <v>3.2684</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>3.2684</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3898</v>
+        <v>2.0309</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1321</v>
+        <v>3.1165</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7423999999999999</v>
+        <v>-1.0856</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3386</v>
+        <v>2.3283</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8876</v>
+        <v>2.8702</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8247</v>
+        <v>3.7882</v>
       </c>
       <c r="K3" t="n">
-        <v>3.0784</v>
+        <v>3.0434</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7463</v>
+        <v>0.7447</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.4861</v>
+        <v>-1.4599</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1908</v>
+        <v>-0.1733</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.2954</v>
+        <v>-1.2866</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2365</v>
+        <v>-0.1184</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4657</v>
+        <v>-0.4441</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7023</v>
+        <v>0.3256</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. GIEDRAITIS</t>
+          <t>F. GUERRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9802</v>
+        <v>1.5231</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1323</v>
+        <v>0.8289</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.152</v>
+        <v>0.6943</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.9457</v>
+        <v>-1.0371</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2884</v>
+        <v>-0.0573</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.2342</v>
+        <v>-0.9798</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9804</v>
+        <v>0.8244</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7619</v>
+        <v>0.6755</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2185</v>
+        <v>0.1489</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.9261</v>
+        <v>-1.8615</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4735</v>
+        <v>-0.7328</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.4526</v>
+        <v>-1.1287</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5789</v>
+        <v>0.2415</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7652</v>
+        <v>0.0531</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1863</v>
+        <v>0.1884</v>
       </c>
       <c r="V4" t="n">
-        <v>3.278</v>
+        <v>1.8634</v>
       </c>
       <c r="W4" t="n">
-        <v>3.278</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1516</v>
+        <v>0.477</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7747</v>
+        <v>2.1056</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6231</v>
+        <v>-1.6287</v>
       </c>
       <c r="G5" t="n">
-        <v>1.737</v>
+        <v>1.7372</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3216</v>
+        <v>0.3298</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4153</v>
+        <v>1.4073</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6741</v>
+        <v>3.6552</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4329</v>
+        <v>0.4309</v>
       </c>
       <c r="L5" t="n">
-        <v>3.2411</v>
+        <v>3.2243</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.9371</v>
+        <v>-1.918</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1113</v>
+        <v>-0.1011</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.8258</v>
+        <v>-1.8169</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4927</v>
+        <v>-0.1707</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7652</v>
+        <v>-0.4114</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2725</v>
+        <v>0.2407</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
@@ -877,49 +877,49 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.129</v>
+        <v>-0.1275</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1463</v>
+        <v>-0.1447</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3559</v>
+        <v>-0.3551</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2424</v>
+        <v>-1.0779</v>
       </c>
       <c r="E7" t="n">
-        <v>0.615</v>
+        <v>0.5762</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.8573</v>
+        <v>-1.654</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9689</v>
+        <v>-0.9923</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2652</v>
+        <v>-0.2861</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7037</v>
+        <v>-0.7062</v>
       </c>
       <c r="J7" t="n">
-        <v>1.349</v>
+        <v>1.2966</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0511</v>
+        <v>0.0163</v>
       </c>
       <c r="L7" t="n">
-        <v>1.298</v>
+        <v>1.2803</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.3179</v>
+        <v>-2.2888</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.0017</v>
+        <v>-1.9865</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5399</v>
+        <v>-0.3635</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4657</v>
+        <v>-0.4441</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0741</v>
+        <v>0.0805</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.9604</v>
+        <v>-1.9497</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. SCRUBB</t>
+          <t>A. DOORNEKAMP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8779</v>
+        <v>-1.8081</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1196</v>
+        <v>-1.3452</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7583</v>
+        <v>-0.4629</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.301</v>
+        <v>-2.4967</v>
       </c>
       <c r="H8" t="n">
-        <v>1.4316</v>
+        <v>-0.7504999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.7326</v>
+        <v>-1.7462</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2021</v>
+        <v>-0.5341</v>
       </c>
       <c r="K8" t="n">
-        <v>1.7001</v>
+        <v>0.2413</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.4981</v>
+        <v>-0.7754</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.503</v>
+        <v>-1.9626</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2685</v>
+        <v>-0.9918</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2345</v>
+        <v>-0.9708</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2268</v>
+        <v>1.3658</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2574</v>
+        <v>-0.6772</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1875</v>
+        <v>-0.5835</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0699</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. DOORNEKAMP</t>
+          <t>T. SCRUBB</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9337</v>
+        <v>-1.9038</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3464</v>
+        <v>-1.1994</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5873</v>
+        <v>-0.7043</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.5045</v>
+        <v>-0.3114</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7665</v>
+        <v>1.4195</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.738</v>
+        <v>-1.7309</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5147</v>
+        <v>0.1737</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2424</v>
+        <v>1.6785</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7572</v>
+        <v>-1.5048</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.9897</v>
+        <v>-0.4851</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0089</v>
+        <v>-0.259</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9808</v>
+        <v>-0.226</v>
       </c>
       <c r="P9" t="n">
-        <v>1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7903</v>
+        <v>-0.2753</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6049</v>
+        <v>-0.2349</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1854</v>
+        <v>-0.0403</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0231</v>
+        <v>-2.092</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2144</v>
+        <v>-2.2374</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1913</v>
+        <v>0.1454</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.6618</v>
+        <v>-2.6703</v>
       </c>
       <c r="H10" t="n">
-        <v>1.2885</v>
+        <v>1.2895</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.9504</v>
+        <v>-3.9598</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.2174</v>
+        <v>-2.2418</v>
       </c>
       <c r="K10" t="n">
-        <v>0.928</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.1454</v>
+        <v>-3.1586</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4444</v>
+        <v>-0.4285</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3605</v>
+        <v>0.3727</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.805</v>
+        <v>-0.8012</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4119</v>
+        <v>0.3507</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2299</v>
+        <v>0.232</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1821</v>
+        <v>0.1187</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8384</v>
+        <v>-2.5017</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5283</v>
+        <v>0.8037</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.3667</v>
+        <v>-3.3054</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9254</v>
+        <v>-0.9304</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5167</v>
+        <v>0.5115</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.442</v>
+        <v>-1.4419</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1262</v>
+        <v>1.1034</v>
       </c>
       <c r="K11" t="n">
-        <v>1.4302</v>
+        <v>1.4167</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3039</v>
+        <v>-0.3132</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.0516</v>
+        <v>-2.0339</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9135</v>
+        <v>-0.9052</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.1381</v>
+        <v>-1.1287</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4328</v>
+        <v>-0.0964</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5565</v>
+        <v>-0.251</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1237</v>
+        <v>0.1546</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8704</v>
+        <v>-4.3467</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3295</v>
+        <v>-1.9337</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.5409</v>
+        <v>-2.4129</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.7144</v>
+        <v>-2.717</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2365</v>
+        <v>0.2465</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.9508</v>
+        <v>-2.9634</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7991</v>
+        <v>-0.8253</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2295</v>
+        <v>1.2238</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.0286</v>
+        <v>-2.0491</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.9152</v>
+        <v>-1.8916</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.993</v>
+        <v>-0.9774</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P12" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5585</v>
+        <v>-1.0442</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.5303</v>
+        <v>-1.1084</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0281</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="13">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.990599999999999</v>
+        <v>-7.299200000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8602</v>
+        <v>3.2598</v>
       </c>
       <c r="F13" t="n">
-        <v>-10.8508</v>
+        <v>-10.5587</v>
       </c>
       <c r="G13" t="n">
-        <v>-8.345599999999999</v>
+        <v>-8.383099999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>5.9017</v>
+        <v>5.888500000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-14.2474</v>
+        <v>-14.2717</v>
       </c>
       <c r="J13" t="n">
-        <v>8.477400000000001</v>
+        <v>8.224</v>
       </c>
       <c r="K13" t="n">
-        <v>10.5574</v>
+        <v>10.4188</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.08</v>
+        <v>-2.1948</v>
       </c>
       <c r="M13" t="n">
-        <v>-16.8228</v>
+        <v>-16.6071</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.6556</v>
+        <v>-4.5305</v>
       </c>
       <c r="O13" t="n">
-        <v>-12.1674</v>
+        <v>-12.0767</v>
       </c>
       <c r="P13" t="n">
-        <v>5.6708</v>
+        <v>5.6908</v>
       </c>
       <c r="Q13" t="n">
-        <v>-7.9392</v>
+        <v>-7.9672</v>
       </c>
       <c r="R13" t="n">
-        <v>13.6099</v>
+        <v>13.6578</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.8734</v>
+        <v>-2.1837</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.234</v>
+        <v>-3.534</v>
       </c>
       <c r="U13" t="n">
-        <v>1.361</v>
+        <v>1.3502</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.4427</v>
+        <v>-2.423099999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>6.5561</v>
+        <v>6.5369</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.998699999999999</v>
+        <v>-8.959900000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. GOLOMAN</t>
+          <t>J. BATEMON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.2448</v>
+        <v>5.0408</v>
       </c>
       <c r="E14" t="n">
-        <v>5.5081</v>
+        <v>4.1265</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2633</v>
+        <v>0.9142</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0492</v>
+        <v>3.6874</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4676</v>
+        <v>-0.8735000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5168</v>
+        <v>4.5609</v>
       </c>
       <c r="J14" t="n">
-        <v>2.1858</v>
+        <v>3.827</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7304</v>
+        <v>0.5064</v>
       </c>
       <c r="L14" t="n">
-        <v>1.4554</v>
+        <v>3.3206</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.1365</v>
+        <v>-0.1396</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.198</v>
+        <v>-1.3799</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0614</v>
+        <v>1.2402</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>-3.4145</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2351</v>
+        <v>0.3613</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4034</v>
+        <v>-0.6439</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8317</v>
+        <v>1.0052</v>
       </c>
       <c r="V14" t="n">
-        <v>1.9604</v>
+        <v>3.2684</v>
       </c>
       <c r="W14" t="n">
-        <v>3.0531</v>
+        <v>4.3579</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. BATEMON</t>
+          <t>G. GOLOMAN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3124</v>
+        <v>4.1924</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6045</v>
+        <v>4.4121</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7079</v>
+        <v>-0.2197</v>
       </c>
       <c r="G15" t="n">
-        <v>3.6883</v>
+        <v>1.065</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8803</v>
+        <v>-0.4654</v>
       </c>
       <c r="I15" t="n">
-        <v>4.5687</v>
+        <v>1.5304</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8703</v>
+        <v>2.1655</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5226</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>3.3477</v>
+        <v>1.4522</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.182</v>
+        <v>-1.1004</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4029</v>
+        <v>-1.1786</v>
       </c>
       <c r="O15" t="n">
-        <v>1.221</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.4025</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3856</v>
+        <v>1.1776</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.234</v>
+        <v>0.3456</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8483000000000001</v>
+        <v>0.832</v>
       </c>
       <c r="V15" t="n">
-        <v>3.278</v>
+        <v>1.9497</v>
       </c>
       <c r="W15" t="n">
-        <v>4.3707</v>
+        <v>3.0392</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. SHURNA</t>
+          <t>C. WALDEN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.3799</v>
+        <v>4.0275</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1871</v>
+        <v>2.5396</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1928</v>
+        <v>1.4879</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6654</v>
+        <v>2.3373</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2325</v>
+        <v>0.4794</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8979</v>
+        <v>1.8579</v>
       </c>
       <c r="J16" t="n">
-        <v>3.426</v>
+        <v>2.9928</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7446</v>
+        <v>2.0027</v>
       </c>
       <c r="L16" t="n">
-        <v>2.6814</v>
+        <v>0.9901</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7606</v>
+        <v>-0.6555</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9771</v>
+        <v>-1.5233</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7835</v>
+        <v>0.8678</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>1.7146</v>
+        <v>0.4218</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8953</v>
+        <v>-0.3558</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8193</v>
+        <v>0.7776</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. WALDEN</t>
+          <t>J. SHURNA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.292</v>
+        <v>2.8362</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7556</v>
+        <v>2.5773</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5364</v>
+        <v>0.259</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3246</v>
+        <v>1.676</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4747</v>
+        <v>-0.2217</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8499</v>
+        <v>1.8978</v>
       </c>
       <c r="J17" t="n">
-        <v>3.0211</v>
+        <v>3.4069</v>
       </c>
       <c r="K17" t="n">
-        <v>2.019</v>
+        <v>0.7412</v>
       </c>
       <c r="L17" t="n">
-        <v>1.0021</v>
+        <v>2.6657</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6965</v>
+        <v>-1.7309</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.5443</v>
+        <v>-0.9629</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8478</v>
+        <v>-0.768</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9073</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3106</v>
+        <v>1.1602</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1825</v>
+        <v>0.3085</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8719</v>
+        <v>0.8517</v>
       </c>
       <c r="V17" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.7837</v>
+        <v>2.3473</v>
       </c>
       <c r="E18" t="n">
-        <v>2.9226</v>
+        <v>2.4397</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1389</v>
+        <v>-0.0924</v>
       </c>
       <c r="G18" t="n">
-        <v>1.9947</v>
+        <v>1.9977</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5281</v>
+        <v>1.5252</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4665</v>
+        <v>0.4725</v>
       </c>
       <c r="J18" t="n">
-        <v>2.5536</v>
+        <v>2.5421</v>
       </c>
       <c r="K18" t="n">
-        <v>2.4417</v>
+        <v>2.4304</v>
       </c>
       <c r="L18" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.5444</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9135</v>
+        <v>-0.9052</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3354</v>
+        <v>-0.1057</v>
       </c>
       <c r="T18" t="n">
-        <v>0.369</v>
+        <v>-0.1024</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0336</v>
+        <v>-0.0033</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0688</v>
+        <v>1.5429</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5105</v>
+        <v>1.0652</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5583</v>
+        <v>0.4777</v>
       </c>
       <c r="G19" t="n">
-        <v>2.4018</v>
+        <v>2.4117</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0129</v>
+        <v>-1.0165</v>
       </c>
       <c r="I19" t="n">
-        <v>3.4147</v>
+        <v>3.4282</v>
       </c>
       <c r="J19" t="n">
-        <v>2.6665</v>
+        <v>2.6383</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6887</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>1.9778</v>
+        <v>1.9736</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2647</v>
+        <v>-0.2266</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.7016</v>
+        <v>-1.6813</v>
       </c>
       <c r="O19" t="n">
-        <v>1.4369</v>
+        <v>1.4547</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1742</v>
+        <v>0.2905</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1825</v>
+        <v>-0.5927</v>
       </c>
       <c r="U19" t="n">
-        <v>1.0083</v>
+        <v>0.8832</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.0089</v>
       </c>
       <c r="E20" t="n">
-        <v>2.076</v>
+        <v>2.176</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.1391</v>
+        <v>-2.1849</v>
       </c>
       <c r="G20" t="n">
-        <v>2.0663</v>
+        <v>2.0654</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5108</v>
+        <v>-1.508</v>
       </c>
       <c r="I20" t="n">
-        <v>3.5771</v>
+        <v>3.5734</v>
       </c>
       <c r="J20" t="n">
-        <v>3.6275</v>
+        <v>3.6139</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.44</v>
+        <v>-0.4449</v>
       </c>
       <c r="L20" t="n">
-        <v>4.0675</v>
+        <v>4.0588</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5612</v>
+        <v>-1.5485</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0708</v>
+        <v>-1.0631</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3563</v>
+        <v>-0.302</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4174</v>
+        <v>-0.2998</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0611</v>
+        <v>-0.0022</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7401</v>
+        <v>-2.8817</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.5589</v>
+        <v>-3.4632</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8189</v>
+        <v>0.5815</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6859</v>
+        <v>-0.6867</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.9999</v>
+        <v>-1.999</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3141</v>
+        <v>1.3123</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8732</v>
+        <v>-0.8871</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2437</v>
+        <v>-1.2518</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3705</v>
+        <v>0.3647</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1874</v>
+        <v>0.2003</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7563</v>
+        <v>-0.7472</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9436</v>
+        <v>0.9476</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0127</v>
+        <v>-0.1462</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4174</v>
+        <v>-0.2998</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4047</v>
+        <v>0.1535</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.53</v>
+        <v>-3.1282</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3842</v>
+        <v>-0.1595</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.1458</v>
+        <v>-2.9687</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.694</v>
+        <v>-1.6937</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7503</v>
+        <v>0.7524</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.4443</v>
+        <v>-2.446</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2632</v>
+        <v>-0.2755</v>
       </c>
       <c r="K22" t="n">
-        <v>1.1602</v>
+        <v>1.1549</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.4234</v>
+        <v>-1.4303</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4308</v>
+        <v>-1.4182</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4099</v>
+        <v>-0.4025</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0209</v>
+        <v>-1.0157</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3312</v>
+        <v>0.0615</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.121</v>
+        <v>0.116</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2102</v>
+        <v>-0.0545</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="23">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.7578</v>
+        <v>-5.9723</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.7705</v>
+        <v>-5.1549</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9873</v>
+        <v>-0.8174</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.4648</v>
+        <v>-4.4771</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.551</v>
+        <v>-2.5613</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.9139</v>
+        <v>-1.9157</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.3913</v>
+        <v>-3.4168</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.9679</v>
+        <v>-1.9865</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.4234</v>
+        <v>-1.4303</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0735</v>
+        <v>-1.0603</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1588</v>
+        <v>-0.0384</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5263</v>
+        <v>0.174</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3675</v>
+        <v>-0.2124</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>7.990499999999999</v>
+        <v>7.996</v>
       </c>
       <c r="E24" t="n">
-        <v>10.8508</v>
+        <v>10.5588</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.8601</v>
+        <v>-2.5628</v>
       </c>
       <c r="G24" t="n">
-        <v>8.345599999999997</v>
+        <v>8.382999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>-5.9019</v>
+        <v>-5.888400000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>14.2475</v>
+        <v>14.2717</v>
       </c>
       <c r="J24" t="n">
-        <v>16.8231</v>
+        <v>16.6071</v>
       </c>
       <c r="K24" t="n">
-        <v>4.6556</v>
+        <v>4.5304</v>
       </c>
       <c r="L24" t="n">
-        <v>12.1676</v>
+        <v>12.0768</v>
       </c>
       <c r="M24" t="n">
-        <v>-8.477399999999999</v>
+        <v>-8.2241</v>
       </c>
       <c r="N24" t="n">
-        <v>-10.5575</v>
+        <v>-10.4189</v>
       </c>
       <c r="O24" t="n">
-        <v>2.0801</v>
+        <v>2.1948</v>
       </c>
       <c r="P24" t="n">
-        <v>-5.6707</v>
+        <v>-5.6907</v>
       </c>
       <c r="Q24" t="n">
-        <v>-13.6101</v>
+        <v>-13.6581</v>
       </c>
       <c r="R24" t="n">
-        <v>7.939300000000001</v>
+        <v>7.967300000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>2.8733</v>
+        <v>2.8806</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.3608</v>
+        <v>-1.3503</v>
       </c>
       <c r="U24" t="n">
-        <v>4.234</v>
+        <v>4.2308</v>
       </c>
       <c r="V24" t="n">
-        <v>2.4425</v>
+        <v>2.423</v>
       </c>
       <c r="W24" t="n">
-        <v>8.9986</v>
+        <v>8.959900000000001</v>
       </c>
       <c r="X24" t="n">
-        <v>-6.5561</v>
+        <v>-6.536899999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104587_W15.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104587_W15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104587_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104587_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104587_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104587_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104587_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.9497</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104587_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104587_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104587_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104587_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104587_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104587_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-8.959900000000001</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104587_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104587_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104587_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104587_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104587_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104587_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104587_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104587_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104587_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104587_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-6.536899999999999</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
